--- a/artfynd/A 37458-2025 artfynd.xlsx
+++ b/artfynd/A 37458-2025 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569637</v>
+        <v>121569635</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645691</v>
+        <v>645692</v>
       </c>
       <c r="R2" t="n">
-        <v>7168054</v>
+        <v>7168022</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569636</v>
+        <v>121569637</v>
       </c>
       <c r="B3" t="n">
-        <v>57476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645700</v>
+        <v>645691</v>
       </c>
       <c r="R3" t="n">
-        <v>7168046</v>
+        <v>7168054</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569635</v>
+        <v>121569636</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645692</v>
+        <v>645700</v>
       </c>
       <c r="R4" t="n">
-        <v>7168022</v>
+        <v>7168046</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 37458-2025 artfynd.xlsx
+++ b/artfynd/A 37458-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569637</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569636</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>